--- a/final_output/March Madness Preview 2026.xlsx
+++ b/final_output/March Madness Preview 2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Software Projects\march-madness-previewer\final_output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2434ef0feffdd206/Documents/Personal Life/Sports/CBB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565DB17C-93B8-4C98-B658-D09FFBAB98ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{565DB17C-93B8-4C98-B658-D09FFBAB98ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703C6182-25FF-456E-B447-BBC402D2D0E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A5B2F9FC-FB27-41D3-9882-716C8D814AE7}"/>
   </bookViews>
@@ -1951,10 +1951,10 @@
     <t>Methodology:</t>
   </si>
   <si>
-    <t>Update team names in cells C7 &amp; C8</t>
+    <t>Updated on 3/16/2026</t>
   </si>
   <si>
-    <t>Updated on 3/16/2026</t>
+    <t>Edit team names in cells C7 &amp; C8 to generate desired matchup</t>
   </si>
 </sst>
 </file>
@@ -2420,10 +2420,10 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2950,8 +2950,8 @@
     <row r="5" spans="1:21" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
-      <c r="C5" s="65" t="s">
-        <v>636</v>
+      <c r="C5" s="64" t="s">
+        <v>635</v>
       </c>
       <c r="U5" s="26"/>
     </row>
@@ -2961,21 +2961,21 @@
       <c r="U6" s="26"/>
     </row>
     <row r="7" spans="1:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="65"/>
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3255,17 +3255,17 @@
       <c r="U12"/>
     </row>
     <row r="14" spans="1:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="64" t="s">
+      <c r="C14" s="65" t="s">
         <v>393</v>
       </c>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="1"/>
@@ -3463,19 +3463,19 @@
       </c>
     </row>
     <row r="21" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="64" t="s">
+      <c r="C21" s="65" t="s">
         <v>390</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
       <c r="T21" s="2"/>
       <c r="U21"/>
     </row>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C28" s="27" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">

--- a/final_output/March Madness Preview 2026.xlsx
+++ b/final_output/March Madness Preview 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2434ef0feffdd206/Documents/Personal Life/Sports/CBB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{565DB17C-93B8-4C98-B658-D09FFBAB98ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703C6182-25FF-456E-B447-BBC402D2D0E2}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{565DB17C-93B8-4C98-B658-D09FFBAB98ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1128EE0-077F-4BE4-809D-CB5F7D8C04DA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A5B2F9FC-FB27-41D3-9882-716C8D814AE7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5B2F9FC-FB27-41D3-9882-716C8D814AE7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="18" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="639">
   <si>
     <t>S Dakota St</t>
   </si>
@@ -1909,9 +1909,6 @@
     <t>https://www.teamrankings.com/ncb/</t>
   </si>
   <si>
-    <t>All data pulled from TeamRankings using webscraping Python script</t>
-  </si>
-  <si>
     <t>Opp. FTA/FGA</t>
   </si>
   <si>
@@ -1927,9 +1924,6 @@
     <t>2HRating</t>
   </si>
   <si>
-    <t>Conditional formatting at the bottom of each table simply reflects national positioning and therefore ranges from 1 to 365 (365 D1 college basketball programs in the country in 2025-26)</t>
-  </si>
-  <si>
     <t>Therefore, "Opponent Rating" is essentially just a Strength of Schedule proxy</t>
   </si>
   <si>
@@ -1939,22 +1933,34 @@
     <t>https://harvardsportsanalysis.org/2011/02/re-examining-the-four-factors-the-case-for-free-throws-made-per-100-possessions/</t>
   </si>
   <si>
-    <t>Kenpom Four Factors (eFG%, TO%, ORb%, FTRate) have been highlighted</t>
-  </si>
-  <si>
-    <t>Decided against including True Shooting because it includes Free Throw efficiency in its formula and would therefore be redundant compared to the combination of eFG% and FTRate</t>
-  </si>
-  <si>
     <t>All "Rating" fields are based on TeamRankings' Predictive Rating model, which is Bayesian-like in that it begins with a preseason prior and iteratively updates as new information is realized - should be comparable to KenPom or EvanMiya ratings</t>
   </si>
   <si>
     <t>Methodology:</t>
   </si>
   <si>
-    <t>Updated on 3/16/2026</t>
+    <t>Conditional formatting at the bottom of each table simply reflects national positioning and therefore ranges from 1 to 365 (365 D1 college basketball programs in the country for the 2025-26 season)</t>
   </si>
   <si>
-    <t>Edit team names in cells C7 &amp; C8 to generate desired matchup</t>
+    <t>Kenpom Four Factors (eFG%, TO%, ORb%, FTRate) have been highlighted:</t>
+  </si>
+  <si>
+    <t>All data pulled from TeamRankings using webscraping Python script:</t>
+  </si>
+  <si>
+    <t>Code repo located here:</t>
+  </si>
+  <si>
+    <t>https://github.com/drewpeterson99/march-madness-previewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data includes all games through: </t>
+  </si>
+  <si>
+    <t>Edit team names in cells C7 &amp; C8 to generate desired matchup comparison</t>
+  </si>
+  <si>
+    <t>Decided against pulling True Shooting % because it includes Free Throw efficiency in its formula and would therefore be redundant compared to the combination of eFG% and FTRate</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2085,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2087,7 +2092,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2106,8 +2111,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2260,12 +2271,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2420,8 +2468,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2440,6 +2492,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2742,76 +2798,81 @@
   <sheetPr>
     <tabColor theme="2"/>
   </sheetPr>
-  <dimension ref="B1:H13"/>
+  <dimension ref="B1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="62" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>633</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>634</v>
       </c>
+      <c r="F4" s="41" t="s">
+        <v>635</v>
+      </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>621</v>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="42" t="s">
+        <v>632</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>518</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="41" t="s">
-        <v>620</v>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>627</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>628</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="42" t="s">
-        <v>631</v>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>629</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C6" s="41" t="s">
-        <v>518</v>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>626</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>629</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>630</v>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>638</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>632</v>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="27" t="s">
+        <v>425</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="27" t="s">
         <v>426</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" xr:uid="{45621A42-3A9E-4371-86F8-EDBB2343AF2B}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{138B9961-3B0F-43EC-A927-9487324CA6B4}"/>
-    <hyperlink ref="H7" r:id="rId3" xr:uid="{DAF33703-DB44-497D-82F8-2F024636F569}"/>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{45621A42-3A9E-4371-86F8-EDBB2343AF2B}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{138B9961-3B0F-43EC-A927-9487324CA6B4}"/>
+    <hyperlink ref="H6" r:id="rId3" xr:uid="{DAF33703-DB44-497D-82F8-2F024636F569}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{04E4FD5E-1AD9-4604-A459-7DCA3CA8A28F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2935,23 +2996,27 @@
         <v>618</v>
       </c>
       <c r="L3" s="25" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M3" s="25" t="s">
         <v>619</v>
       </c>
       <c r="U3" s="26"/>
     </row>
-    <row r="4" spans="1:21" s="25" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" s="25" customFormat="1" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
       <c r="B4" s="33"/>
       <c r="U4" s="26"/>
     </row>
-    <row r="5" spans="1:21" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" s="25" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
-      <c r="C5" s="64" t="s">
-        <v>635</v>
+      <c r="C5" s="65" t="s">
+        <v>636</v>
+      </c>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67">
+        <v>46096</v>
       </c>
       <c r="U5" s="26"/>
     </row>
@@ -2961,21 +3026,21 @@
       <c r="U6" s="26"/>
     </row>
     <row r="7" spans="1:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="64" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="65"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="65"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3025,55 +3090,55 @@
         <v>422</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>12</v>
+        <v>435</v>
       </c>
       <c r="D9" s="37">
         <f t="shared" ref="D9:O12" si="0">INDEX(Data, MATCH($C9, Teams, 0), MATCH($A9&amp;D$1, Columns, 0))</f>
-        <v>27.6</v>
+        <v>7.7</v>
       </c>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
-        <v>0.56799999999999995</v>
+        <v>0.51</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>0.55799999999999994</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="G9" s="21">
         <f t="shared" si="0"/>
-        <v>0.46200000000000002</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="H9" s="19">
         <f t="shared" si="0"/>
-        <v>1.198</v>
+        <v>1.111</v>
       </c>
       <c r="I9" s="19">
         <f t="shared" si="0"/>
-        <v>0.91900000000000004</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="0"/>
-        <v>0.55700000000000005</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="K9" s="21">
         <f t="shared" si="0"/>
-        <v>0.41699999999999998</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="L9" s="4">
         <f t="shared" si="0"/>
-        <v>0.36499999999999999</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="M9" s="23">
         <f t="shared" si="0"/>
-        <v>0.77900000000000003</v>
+        <v>0.68299999999999994</v>
       </c>
       <c r="N9" s="16">
         <f t="shared" si="0"/>
-        <v>1.601</v>
+        <v>1.369</v>
       </c>
       <c r="O9" s="16">
         <f t="shared" si="0"/>
-        <v>0.95699999999999996</v>
+        <v>0.745</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9"/>
@@ -3083,55 +3148,55 @@
         <v>422</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="D10" s="38">
         <f t="shared" si="0"/>
-        <v>-1.3</v>
+        <v>14.8</v>
       </c>
       <c r="E10" s="5">
         <f t="shared" si="0"/>
-        <v>0.50600000000000001</v>
+        <v>0.55299999999999994</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" si="0"/>
-        <v>0.49399999999999999</v>
+        <v>0.55899999999999994</v>
       </c>
       <c r="G10" s="22">
         <f t="shared" si="0"/>
-        <v>0.48599999999999999</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="0"/>
-        <v>1.071</v>
+        <v>1.169</v>
       </c>
       <c r="I10" s="20">
         <f t="shared" si="0"/>
-        <v>0.997</v>
+        <v>1.069</v>
       </c>
       <c r="J10" s="5">
         <f t="shared" si="0"/>
-        <v>0.51300000000000001</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="K10" s="22">
         <f t="shared" si="0"/>
-        <v>0.46200000000000002</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="0"/>
-        <v>0.30299999999999999</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="M10" s="22">
         <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="0"/>
-        <v>1.2989999999999999</v>
+        <v>1.6890000000000001</v>
       </c>
       <c r="O10" s="17">
         <f t="shared" si="0"/>
-        <v>1.0369999999999999</v>
+        <v>1.002</v>
       </c>
       <c r="T10" s="2"/>
       <c r="U10"/>
@@ -3142,55 +3207,55 @@
       </c>
       <c r="C11" s="31" t="str">
         <f>C9</f>
-        <v>Duke</v>
+        <v>McNeese</v>
       </c>
       <c r="D11" s="39">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="E11" s="29">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="F11" s="29">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="G11" s="30">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H11" s="29">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="I11" s="29">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J11" s="29">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="K11" s="30">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L11" s="29">
         <f>INDEX(Data, MATCH($C11, Teams, 0), MATCH($A11&amp;L$1, Columns, 0))</f>
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M11" s="30">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>312</v>
       </c>
       <c r="N11" s="29">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="O11" s="29">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="T11" s="2"/>
       <c r="U11"/>
@@ -3201,71 +3266,71 @@
       </c>
       <c r="C12" s="31" t="str">
         <f>C10</f>
-        <v>Siena</v>
+        <v>NC State</v>
       </c>
       <c r="D12" s="39">
         <f t="shared" si="0"/>
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="E12" s="29">
         <f t="shared" si="0"/>
-        <v>214</v>
+        <v>35</v>
       </c>
       <c r="F12" s="29">
         <f t="shared" si="0"/>
-        <v>212</v>
+        <v>11</v>
       </c>
       <c r="G12" s="30">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>271</v>
       </c>
       <c r="H12" s="29">
         <f t="shared" si="0"/>
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="I12" s="29">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="J12" s="29">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="K12" s="30">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="L12" s="29">
         <f t="shared" si="0"/>
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="M12" s="30">
         <f t="shared" si="0"/>
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="N12" s="29">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="O12" s="29">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="T12" s="2"/>
       <c r="U12"/>
     </row>
     <row r="14" spans="1:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="64" t="s">
         <v>393</v>
       </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="1"/>
@@ -3304,39 +3369,39 @@
       </c>
       <c r="C16" s="1" t="str">
         <f>C9</f>
-        <v>Duke</v>
+        <v>McNeese</v>
       </c>
       <c r="D16" s="45">
         <f t="shared" ref="D16:K19" si="1">INDEX(Data, MATCH($C16, Teams, 0), MATCH($A16&amp;D$2, Columns, 0))</f>
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="E16" s="11">
         <f t="shared" si="1"/>
-        <v>82.3</v>
+        <v>76.8</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="1"/>
-        <v>63.1</v>
+        <v>67</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="1"/>
-        <v>0.153</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="1"/>
-        <v>0.17699999999999999</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="I16" s="8">
         <f t="shared" si="1"/>
-        <v>0.33100000000000002</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" si="1"/>
-        <v>0.35099999999999998</v>
+        <v>0.316</v>
       </c>
       <c r="K16" s="4">
         <f t="shared" si="1"/>
-        <v>0.30399999999999999</v>
+        <v>0.32500000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3345,39 +3410,39 @@
       </c>
       <c r="C17" s="53" t="str">
         <f>C10</f>
-        <v>Siena</v>
+        <v>NC State</v>
       </c>
       <c r="D17" s="18">
         <f t="shared" si="1"/>
-        <v>65.900000000000006</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="E17" s="12">
         <f t="shared" si="1"/>
-        <v>70.5</v>
+        <v>83.7</v>
       </c>
       <c r="F17" s="12">
         <f t="shared" si="1"/>
-        <v>65.7</v>
+        <v>76.5</v>
       </c>
       <c r="G17" s="9">
         <f t="shared" si="1"/>
-        <v>0.157</v>
+        <v>0.129</v>
       </c>
       <c r="H17" s="5">
         <f t="shared" si="1"/>
-        <v>0.16700000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="1"/>
-        <v>0.22900000000000001</v>
+        <v>0.371</v>
       </c>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>0.30399999999999999</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="K17" s="5">
         <f t="shared" si="1"/>
-        <v>0.32800000000000001</v>
+        <v>0.35599999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
@@ -3386,39 +3451,39 @@
       </c>
       <c r="C18" s="52" t="str">
         <f>C9</f>
-        <v>Duke</v>
+        <v>McNeese</v>
       </c>
       <c r="D18" s="28">
         <f t="shared" si="1"/>
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="E18" s="29">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="F18" s="29">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G18" s="28">
         <f t="shared" si="1"/>
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="H18" s="29">
         <f t="shared" si="1"/>
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="I18" s="28">
         <f t="shared" si="1"/>
-        <v>133</v>
+        <v>318</v>
       </c>
       <c r="J18" s="29">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>299</v>
       </c>
       <c r="K18" s="29">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
@@ -3427,55 +3492,55 @@
       </c>
       <c r="C19" s="52" t="str">
         <f>C10</f>
-        <v>Siena</v>
+        <v>NC State</v>
       </c>
       <c r="D19" s="28">
         <f t="shared" si="1"/>
-        <v>359</v>
+        <v>121</v>
       </c>
       <c r="E19" s="29">
         <f t="shared" si="1"/>
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="F19" s="29">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>230</v>
       </c>
       <c r="G19" s="28">
         <f t="shared" si="1"/>
-        <v>141</v>
+        <v>9</v>
       </c>
       <c r="H19" s="29">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="I19" s="28">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>46</v>
       </c>
       <c r="J19" s="29">
         <f t="shared" si="1"/>
-        <v>334</v>
+        <v>10</v>
       </c>
       <c r="K19" s="29">
         <f t="shared" si="1"/>
-        <v>106</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
       <c r="T21" s="2"/>
       <c r="U21"/>
     </row>
@@ -3488,7 +3553,7 @@
         <v>612</v>
       </c>
       <c r="F22" s="61" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G22" s="43" t="s">
         <v>614</v>
@@ -3506,7 +3571,7 @@
         <v>523</v>
       </c>
       <c r="L22" s="43" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M22" s="43" t="s">
         <v>289</v>
@@ -3522,47 +3587,47 @@
       </c>
       <c r="C23" s="15" t="str">
         <f>C16</f>
-        <v>Duke</v>
+        <v>McNeese</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" ref="D23:E26" si="2">INDEX(Data, MATCH($C23, Teams, 0), MATCH($A23&amp;D$3, Columns, 0))</f>
-        <v>0.72400000000000009</v>
+        <v>0.74</v>
       </c>
       <c r="E23" s="16">
         <f t="shared" si="2"/>
-        <v>0.378</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="F23" s="56">
         <f t="shared" ref="F23:M26" si="3">INDEX(Data, MATCH($C23, Teams, 0), MATCH($A23&amp;F$3, Columns, 0))</f>
-        <v>0.23699999999999999</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="G23" s="11">
         <f t="shared" si="3"/>
-        <v>15.2</v>
+        <v>-0.1</v>
       </c>
       <c r="H23" s="11">
         <f t="shared" si="3"/>
-        <v>16.600000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I23" s="11">
         <f t="shared" si="3"/>
-        <v>24.9</v>
+        <v>13.6</v>
       </c>
       <c r="J23" s="2">
         <f t="shared" si="3"/>
-        <v>32.700000000000003</v>
+        <v>9.4</v>
       </c>
       <c r="K23" s="45">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L23" s="11">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="M23" s="4">
         <f t="shared" si="3"/>
-        <v>0.71399999999999997</v>
+        <v>0.75</v>
       </c>
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
@@ -3575,47 +3640,47 @@
       </c>
       <c r="C24" s="14" t="str">
         <f>C17</f>
-        <v>Siena</v>
+        <v>NC State</v>
       </c>
       <c r="D24" s="9">
         <f t="shared" si="2"/>
-        <v>0.76900000000000002</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E24" s="17">
         <f t="shared" si="2"/>
-        <v>0.34200000000000003</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="F24" s="57">
         <f t="shared" si="3"/>
-        <v>0.27200000000000002</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="G24" s="12">
         <f t="shared" si="3"/>
-        <v>-5.0999999999999996</v>
+        <v>10.7</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="3"/>
-        <v>-3.6</v>
+        <v>7.4</v>
       </c>
       <c r="I24" s="12">
         <f t="shared" si="3"/>
-        <v>2.2999999999999998</v>
+        <v>15.4</v>
       </c>
       <c r="J24" s="49">
         <f t="shared" si="3"/>
-        <v>-2.2999999999999998</v>
+        <v>8</v>
       </c>
       <c r="K24" s="18">
         <f t="shared" si="3"/>
-        <v>1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="L24" s="12">
         <f t="shared" si="3"/>
-        <v>-0.1</v>
+        <v>7.6</v>
       </c>
       <c r="M24" s="5">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
@@ -3628,47 +3693,47 @@
       </c>
       <c r="C25" s="31" t="str">
         <f>C16</f>
-        <v>Duke</v>
+        <v>McNeese</v>
       </c>
       <c r="D25" s="29">
         <f t="shared" si="2"/>
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="2"/>
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="F25" s="30">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>325</v>
       </c>
       <c r="G25" s="32">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="H25" s="32">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="I25" s="32">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="J25" s="2">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="K25" s="46">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="L25" s="32">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="M25" s="29">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
@@ -3681,47 +3746,47 @@
       </c>
       <c r="C26" s="31" t="str">
         <f>C17</f>
-        <v>Siena</v>
+        <v>NC State</v>
       </c>
       <c r="D26" s="29">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="2"/>
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="F26" s="30">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>226</v>
       </c>
       <c r="G26" s="32">
         <f t="shared" si="3"/>
-        <v>274</v>
+        <v>36</v>
       </c>
       <c r="H26" s="32">
         <f t="shared" si="3"/>
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="I26" s="32">
         <f t="shared" si="3"/>
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="J26" s="2">
         <f t="shared" si="3"/>
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="K26" s="46">
         <f t="shared" si="3"/>
-        <v>93</v>
+        <v>301</v>
       </c>
       <c r="L26" s="32">
         <f t="shared" si="3"/>
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="M26" s="29">
         <f t="shared" si="3"/>
-        <v>97</v>
+        <v>328</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -3734,12 +3799,12 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C28" s="27" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C29" s="63" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -3760,7 +3825,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C10" xr:uid="{D944E4A1-6C61-4E2B-8EBC-8D0FB1434C5C}">
       <formula1>Top200Teams</formula1>
     </dataValidation>
@@ -3876,10 +3941,10 @@
         <v>544</v>
       </c>
       <c r="L1" s="58" t="s">
+        <v>623</v>
+      </c>
+      <c r="M1" s="58" t="s">
         <v>624</v>
-      </c>
-      <c r="M1" s="58" t="s">
-        <v>625</v>
       </c>
       <c r="N1" s="58" t="s">
         <v>545</v>
